--- a/survey_templates/044_debrief_survey--survey_templates.xlsx
+++ b/survey_templates/044_debrief_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction_to_debrief_survey</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A brief welcome message to users.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>team_members</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Team members</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>List the team members who were present during the event.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -571,10 +579,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>feedback_on_event_or_project</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Provide detailed feedback about the event or project.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -589,12 +601,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ratings</t>
+          <t>effectiveness_rating</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>overall_effectiveness_rating</t>
+          <t>Overall Effectiveness Rating</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,10 +629,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>what_to_improve</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Recommendations</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Suggest improvements for future events or projects.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -640,10 +656,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>additional_comments</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Provide any additional comments or notes.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -658,12 +678,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>conclusion_page</t>
+          <t>form_version</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>conclusion</t>
+          <t>Form Version</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +696,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>form_id</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>Form ID</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +724,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>assigned_user</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>assigned_user</t>
+          <t>Created By</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +747,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>team_name</t>
+          <t>updated_by</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>team_name</t>
+          <t>Updated By</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +765,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>event_name</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>event_name</t>
+          <t>Updated At</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,269 +793,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_version_id</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Form Id</t>
+          <t>Form Version ID</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>created_by</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Created At</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Updated At</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>form_version</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Form Version</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>form_version_id</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Form Version Id</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>created_by</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>created_by</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>updated_by</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>updated_by</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1052,12 +819,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1085,12 +852,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
@@ -1102,12 +869,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>event_coordinator</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Event Coordinator</t>
         </is>
       </c>
     </row>
@@ -1119,114 +886,97 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>project_manager</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Project Manager</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ratings_choices</t>
+          <t>team_members_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ratings_choices</t>
+          <t>team_members_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ratings_choices</t>
+          <t>effectiveness_rating_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>highly_effective</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Highly effective</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>submit_choices</t>
+          <t>effectiveness_rating_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>somewhat_effective</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Somewhat effective</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>submit_choices</t>
+          <t>effectiveness_rating_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>not_effective</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>submit_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>option3</t>
+          <t>Not effective</t>
         </is>
       </c>
     </row>
